--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:48:16+00:00</t>
+    <t>2026-02-23T18:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:02:53+00:00</t>
+    <t>2026-02-24T08:32:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T08:32:52+00:00</t>
+    <t>2026-02-26T16:12:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:12:14+00:00</t>
+    <t>2026-02-27T13:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:39:19+00:00</t>
+    <t>2026-02-27T14:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T14:39:40+00:00</t>
+    <t>2026-02-27T15:25:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-task-moyen-ressource.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:25:53+00:00</t>
+    <t>2026-02-27T15:59:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
